--- a/data/source/xlsx/Witnesses.xlsx
+++ b/data/source/xlsx/Witnesses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,21 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Display_Label</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Read_In</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Page_Range</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -514,7 +529,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Redazione in rivista, in cinque puntate: fascicoli 26, 27, 28, 29 e 31 del 1946, senza il n. 30 (Pinotti 2016, p. 200, n. 4; Pinotti 2024, § 7.2). Citata da RR II, pp. 277–460.</t>
+          <t>Redazione in rivista, in cinque puntate: fascicoli 26, 27, 28, 29 e 31 del 1946, senza il n. 30 (Pinotti 2016, p. 200, n. 4; Pinotti 2024, § 7.2). Letta in RR II, pp. 277–460: le pagine di QPL nelle occorrenze sono pagine di RR II.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>rr2</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>277–460</t>
         </is>
       </c>
     </row>
@@ -585,12 +610,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>qp57</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QP57</t>
+          <t>QP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -615,7 +640,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Princeps Garzanti: finito di stampare del 22 giugno 1957. Nuovi capitoli consegnati fra il 23 aprile 1955 e il 6 febbraio 1957; il romanesco dei «tratti» di rivista rivisto con Dell'Arco, il quarto sacrificato, il tutto riorganizzato in dieci capitoli (Matt e Pinotti 2022, pp. 271–272).</t>
+          <t>Versione in volume: princeps Garzanti, finito di stampare del 22 giugno 1957. Nuovi capitoli consegnati fra il 23 aprile 1955 e il 6 febbraio 1957; il romanesco dei «tratti» di rivista rivisto con Dell'Arco, il quarto sacrificato, il tutto riorganizzato in dieci capitoli (Matt e Pinotti 2022, pp. 271–272). Letta in RR II: le pagine di QP nelle occorrenze sono pagine di RR II (D-073).</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -626,18 +651,23 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>Matt e Pinotti 2022, pp. 271–272 (revisione dei «tratti» di rivista); Cap. 4, n. 10 (bzFG = bozze del volume)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>rr2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rr2</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RR II</t>
+          <t>QPa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -651,66 +681,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1989</v>
+        <v>2018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giorgio Pinotti, Dante Isella, Raffaella Rodondi</t>
+          <t>Giorgio Pinotti</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Garzanti, Milano</t>
+          <t>Adelphi, Milano</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C. E. Gadda, Romanzi e racconti II, in Opere di Carlo Emilio Gadda. Edizione da cui citano Manzotti 2010, Pinotti 2016 e Perosa 2023a.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>qp</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>QP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>quer_pasticciaccio</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>edizione</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Giorgio Pinotti</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Adelphi, Milano</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Edizione di riferimento della tesi, nel volume a stampa. La copia digitale ha almeno una lezione non emendata.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+          <t>Ristampa Adelphi 2018 a cura di Giorgio Pinotti: testo di riferimento del progetto, nel volume a stampa, su cui sono annotate le occorrenze. La copia digitale ha almeno una lezione non emendata.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>si</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>QP (Adelphi 2018)</t>
         </is>
       </c>
     </row>
